--- a/floristics_data/abundance_data/abundance_metadata.xlsx
+++ b/floristics_data/abundance_data/abundance_metadata.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gwenr\Documents\Git\junction_floristics\floristics_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gwenr\Documents\Git\junction_floristics\floristics_data\abundance_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C27878D-61F2-4EA2-96EF-CC97EA2F71FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E337D6-B0BB-428E-AB52-5275679A182B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{B8FD48B8-081A-410A-B965-6C2661207FB2}"/>
   </bookViews>
@@ -39,10 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
-  <si>
-    <t>sheet</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>column_name</t>
   </si>
@@ -56,9 +53,6 @@
     <t>The name of the transect. Composed of whether the specimen was collected at South Llano River State Park or TTU Center at Junction as well as the unique number assigned to it.</t>
   </si>
   <si>
-    <t>abundance_data</t>
-  </si>
-  <si>
     <t>transect</t>
   </si>
   <si>
@@ -134,7 +128,7 @@
     <t>"JUNC-0096, JUNC-0204", "none"</t>
   </si>
   <si>
-    <t>The collection number for a specimen collected on/around that transect that was recorded using the same description as the species listed in the data, or a picture of the species listed in the data along with the file name (which can be accessed by contacting the author Gwendolyn Watt). If there was no corresponding collection or picture, "none" was listed. "N/A" was entered for rock, bareground, and litter entries.</t>
+    <t>The collection number for a specimen collected on/around that transect that was recorded using the same description as the species listed in the data, or a picture of the species listed in the data along with the file name. If there was no corresponding collection or picture, "none" was listed. "N/A" was entered for rock, bareground, and litter entries.</t>
   </si>
 </sst>
 </file>
@@ -470,16 +464,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FD5CA88-8B11-42EB-BAAE-BF222B2063B5}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="14.734375" customWidth="1"/>
-    <col min="2" max="2" width="32.05078125" customWidth="1"/>
-    <col min="3" max="3" width="51.5234375" customWidth="1"/>
-    <col min="4" max="4" width="54.62890625" customWidth="1"/>
+    <col min="1" max="1" width="32.05078125" customWidth="1"/>
+    <col min="2" max="2" width="51.5234375" customWidth="1"/>
+    <col min="3" max="3" width="54.62890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -489,134 +482,104 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:3" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="57.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:3" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="D4" t="s">
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="57.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="D5" t="s">
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="2" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
         <v>18</v>
       </c>
-      <c r="D6" t="s">
+      <c r="B7" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
         <v>21</v>
       </c>
-      <c r="D7" t="s">
+      <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="2" t="s">
+    </row>
+    <row r="9" spans="1:3" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
         <v>24</v>
       </c>
-      <c r="D8" t="s">
+      <c r="B9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="100.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" t="s">
+    <row r="10" spans="1:3" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="B10" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="100.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>28</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
